--- a/backtest_runs/20260410_193731/by_symbol/TRG/TRG.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TRG/TRG.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-2530.709999999988</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>97469.29000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>97469.29000000001</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>97469.29000000001</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>97469.29000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-3287.759999999992</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>97923.52000000002</v>
@@ -1185,7 +1185,7 @@
         <v>-4261.109999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>98118.19</v>
@@ -1231,7 +1231,7 @@
         <v>-237.9299999999988</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>97880.26000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-735.419999999992</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>97144.84000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-151.4100000000006</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>96993.43000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-5623.800000000003</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>122084.23</v>
